--- a/docs/function_list.xlsx
+++ b/docs/function_list.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\GitHub\SpringBoot_Controller-Service-DAO\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11FEA796-BFE6-4384-904F-EF2DD24FE6D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EACFF777-EE89-4FA5-AAA8-EF97BF560F59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5595" yWindow="4200" windowWidth="24015" windowHeight="14445" xr2:uid="{2AB0222D-0F61-4210-99DF-869CD227FA90}"/>
+    <workbookView xWindow="3240" yWindow="1155" windowWidth="24015" windowHeight="14445" xr2:uid="{2AB0222D-0F61-4210-99DF-869CD227FA90}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -54,9 +54,6 @@
     <t>Payment - Enquiry by pk</t>
   </si>
   <si>
-    <t>payment-get-payment-details-by-pk</t>
-  </si>
-  <si>
     <t>{
     "checkNumber" : "String"
 }</t>
@@ -68,6 +65,9 @@
     "paymentDate": string
     "amount": double
 }</t>
+  </si>
+  <si>
+    <t>/payment/get-payment-details-by-pk</t>
   </si>
 </sst>
 </file>
@@ -477,13 +477,13 @@
         <v>5</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>7</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>8</v>
       </c>
     </row>
   </sheetData>
